--- a/output/pdf_financials_xlsx/GOT.xlsx
+++ b/output/pdf_financials_xlsx/GOT.xlsx
@@ -889,25 +889,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.03112</v>
+        <v>0.083116</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.033994</v>
+        <v>0.088944</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.035146</v>
+        <v>0.213123</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.03352</v>
+        <v>0.101364</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.033116</v>
+        <v>0.085964</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.017663</v>
+        <v>0.100489</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.01672</v>
+        <v>0.151012</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0</v>
@@ -944,25 +944,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.03112</v>
+        <v>-0.083116</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.033994</v>
+        <v>-0.088944</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.035146</v>
+        <v>-0.213123</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.03352</v>
+        <v>-0.101364</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.033116</v>
+        <v>-0.085964</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.017663</v>
+        <v>-0.100489</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.01672</v>
+        <v>-0.151012</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>0</v>
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1008,16 +1008,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>6.7e-05</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>1.1e-05</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.08311300000000001</v>
+        <v>-0.083116</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.088944</v>
@@ -1899,16 +1899,16 @@
         <v>-0.213123</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.101297</v>
+        <v>-0.101364</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.085953</v>
+        <v>-0.085964</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.100487</v>
+        <v>-0.100489</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.151009</v>
+        <v>-0.151012</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.921056</v>
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.08311300000000001</v>
+        <v>-0.083116</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.088944</v>
@@ -2009,16 +2009,16 @@
         <v>-0.213123</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.101297</v>
+        <v>-0.101364</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.085953</v>
+        <v>-0.085964</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.100487</v>
+        <v>-0.100489</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.151009</v>
+        <v>-0.151012</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.921056</v>
@@ -2291,37 +2291,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.667673</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.500922</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.301251</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.227917</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.121163</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.022592</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000937</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.357369</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.810737</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.896054</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.026131</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>5.025438</v>
@@ -2401,37 +2401,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.667673</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.500922</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.301251</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.227917</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.121163</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.022592</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000937</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.357369</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.810737</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.896054</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.026131</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>5.025438</v>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -23068,7 +23068,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
@@ -23806,7 +23806,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">

--- a/output/pdf_financials_xlsx/GOT.xlsx
+++ b/output/pdf_financials_xlsx/GOT.xlsx
@@ -6695,10 +6695,10 @@
         <v>0</v>
       </c>
       <c r="O111" s="3" t="n">
-        <v>0</v>
+        <v>-0.200901</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.022684</v>
       </c>
       <c r="Q111" s="3" t="n">
         <v>0</v>
@@ -6866,7 +6866,7 @@
         <v>0</v>
       </c>
       <c r="Q114" s="3" t="n">
-        <v>0</v>
+        <v>1.223954</v>
       </c>
     </row>
     <row r="115">
@@ -8060,10 +8060,10 @@
         <v>0</v>
       </c>
       <c r="O134" s="3" t="n">
-        <v>0</v>
+        <v>-0.200901</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.022684</v>
       </c>
       <c r="Q134" s="3" t="n">
         <v>0</v>
@@ -13138,7 +13138,11 @@
           <t>Loss on acquisition of investments</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -13870,7 +13874,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14840,7 +14848,11 @@
           <t>Investments acquired in private placement $</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
